--- a/data/references/all_teams.xlsx
+++ b/data/references/all_teams.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Vincent\eclipse\workspaces\Test\RugbyScope\RugbyScope\data\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517F92CE-C2AC-4D95-8F62-480813D75387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7225B58-8E9A-450A-80D7-4A22637225B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="11" xr2:uid="{AE175A19-926C-4360-A043-3AD9C14161A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{AE175A19-926C-4360-A043-3AD9C14161A6}"/>
   </bookViews>
   <sheets>
     <sheet name="AR" sheetId="10" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13876" uniqueCount="7579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13877" uniqueCount="7579">
   <si>
     <t>Bargoed RFC</t>
   </si>
@@ -85323,7 +85323,7 @@
         <v>7113</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
         <v>1470</v>
       </c>
@@ -85334,7 +85334,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
         <v>1471</v>
       </c>
@@ -85345,7 +85345,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
         <v>1472</v>
       </c>
@@ -85356,7 +85356,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
         <v>1473</v>
       </c>
@@ -85367,7 +85367,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
         <v>329</v>
       </c>
@@ -85377,8 +85377,11 @@
       <c r="C181" s="3" t="s">
         <v>1545</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E181" s="3" t="s">
+        <v>6750</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
         <v>1474</v>
       </c>
@@ -85389,7 +85392,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
         <v>1475</v>
       </c>
@@ -85400,7 +85403,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
         <v>1461</v>
       </c>
@@ -85411,7 +85414,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
         <v>1462</v>
       </c>
@@ -85422,7 +85425,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
         <v>1463</v>
       </c>
@@ -85433,7 +85436,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
         <v>1464</v>
       </c>
@@ -85444,7 +85447,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
         <v>1465</v>
       </c>
@@ -85455,7 +85458,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
         <v>7056</v>
       </c>
@@ -85466,7 +85469,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
         <v>7057</v>
       </c>
@@ -85477,7 +85480,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
         <v>7058</v>
       </c>
@@ -85488,7 +85491,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
         <v>1602</v>
       </c>
